--- a/docs/export-templates/AI问书_全域知识产品数据导出.xlsx
+++ b/docs/export-templates/AI问书_全域知识产品数据导出.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="78">
   <si>
     <t>平台全域知识产品 KP</t>
   </si>
@@ -190,7 +190,7 @@
     <t>围手术期麻醉管理精要</t>
   </si>
   <si>
-    <t>unlisted</t>
+    <t>已下架</t>
   </si>
   <si>
     <t>永享 ¥29</t>
@@ -202,13 +202,28 @@
     <t>术前评估 / 麻醉方案 / 术后镇痛，覆盖 40+ 高危场景处置。</t>
   </si>
   <si>
+    <t>kp_icu_manual</t>
+  </si>
+  <si>
+    <t>危重症监护实践手册</t>
+  </si>
+  <si>
+    <t>永享 ¥39</t>
+  </si>
+  <si>
+    <t>2026-03-08</t>
+  </si>
+  <si>
+    <t>ICU 常见危象识别与处置流程，含 30+ 床旁操作视频。</t>
+  </si>
+  <si>
     <t>kp_ultrasound_old</t>
   </si>
   <si>
     <t>急诊超声快速上手（旧版）</t>
   </si>
   <si>
-    <t>已下架</t>
+    <t>已删除</t>
   </si>
   <si>
     <t>永享 ¥19</t>
@@ -217,7 +232,7 @@
     <t>2025-11-20</t>
   </si>
   <si>
-    <t>旧版内容已由新版替代，本 KP 已归档下线。</t>
+    <t>旧版内容已由新版替代，本 KP 已删除下线。</t>
   </si>
   <si>
     <t>kp_demo_deletable</t>
@@ -229,7 +244,7 @@
     <t>2026-07-10</t>
   </si>
   <si>
-    <t>刚创建、尚未上架，无任何订单 / 赠送 / 分享 / 导入关系，可被物理删除。</t>
+    <t>刚创建、尚未上架，无任何订单 / 赠送 / 分享 / 导入关系。</t>
   </si>
 </sst>
 </file>
@@ -696,7 +711,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -1016,45 +1031,71 @@
         <v>13</v>
       </c>
       <c r="D14" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="E14" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="E14" s="7" t="s">
+      <c r="F14" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G14" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="F14" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="G14" s="7" t="s">
+      <c r="H14" s="7" t="s">
         <v>67</v>
-      </c>
-      <c r="H14" s="7" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B15" s="5" t="s">
         <v>69</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>70</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>13</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>33</v>
+        <v>71</v>
       </c>
       <c r="F15" s="5" t="s">
         <v>16</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
+      </c>
+    </row>
+    <row r="16" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H16" s="7" t="s">
+        <v>77</v>
       </c>
     </row>
   </sheetData>
